--- a/data/output/2025/evaluasi_35.xlsx
+++ b/data/output/2025/evaluasi_35.xlsx
@@ -42,6 +42,10 @@
     <sheet name="3575" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="3579" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="3578" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="3502" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="3523" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="3576" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="3522" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -673,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,6 +765,62 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3521</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngawi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8493230776250598</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3521</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngawi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -775,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +895,174 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9701169566177817</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>40.51148475625742</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.064225466898211</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.6962262611005</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1315061675389107</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -849,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,6 +1137,174 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.334457210709355</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1174783644437367</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>55.80163566237676</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.430207521590947</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.218987047930005</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -923,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,6 +1379,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulungagung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.875561311298489</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulungagung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1391707841625376</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulungagung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>47.91216287904548</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulungagung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulungagung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.212236307137281</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -997,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,18 +1663,158 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>1.966208812700808</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3505</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Blitar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.296199540482326</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3505</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Blitar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>61.88182600288805</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3505</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Blitar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3505</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Blitar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.034873712841098</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3505</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Blitar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>-3.59418613123904</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1155,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1891,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.665479100526595</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.205087730692958</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>41.29975015101325</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.27256602616712</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.474236638040963</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.544926208959697</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.041799738237214</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1229,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,6 +2245,202 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.605462444509905</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>19.60482542794473</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.935289049680054</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.012100072663027</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.308225564796159</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.521534829185549</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1359,7 +2455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1531,6 +2627,174 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3510</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyuwangi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.571363252105133</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3510</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyuwangi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.629199459652031</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3510</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyuwangi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>38.91082435505734</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3510</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyuwangi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3510</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyuwangi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.765628282248251</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3510</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyuwangi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.423216876198701</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1545,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1927,20 +3191,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2.630943041497784</v>
+        <v>38.87713239979988</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1955,18 +3219,158 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3511</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bondowoso</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.25689452011002</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3511</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Bondowoso</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.076479110536438</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3511</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Bondowoso</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2173628695748703</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3511</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Bondowoso</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.630943041497784</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3511</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Bondowoso</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>-3.070061600204918</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1983,7 +3387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2197,20 +3601,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3.468073849096316</v>
+        <v>1.772315587737631</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2225,20 +3629,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-7.286889123872907</v>
+        <v>0.1183138682327946</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2253,18 +3657,186 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>23.21522896918742</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3512</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Situbondo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3512</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Situbondo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>17.48349232722577</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3512</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Situbondo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>21.45387554196444</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3512</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Situbondo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-3.468073849096316</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3512</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Situbondo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-7.286889123872907</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3512</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Situbondo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>-6.140461115278876</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2281,7 +3853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2565,6 +4137,118 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3577</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Madiun</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.412538649127577</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3577</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Madiun</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3577</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Madiun</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.035948222480911</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3577</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Madiun</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.091858327092898</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2579,7 +4263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2639,6 +4323,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3514</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasuruan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2653,7 +4365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,6 +4453,146 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3515</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidoarjo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-10.17437941806377</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3515</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidoarjo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3515</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidoarjo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.9299926374966319</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3515</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidoarjo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.910809312531143</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3515</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidoarjo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.539522766390501</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2755,7 +4607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2815,6 +4667,90 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3516</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Mojokerto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-8.664881794003096</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3516</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mojokerto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3516</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mojokerto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.6416685666619188</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2829,7 +4765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2945,6 +4881,90 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3517</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Jombang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3517</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Jombang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.92789485933314</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3517</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Jombang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1114024910823039</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2959,7 +4979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3019,6 +5039,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3518</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Nganjuk</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3033,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3093,6 +5141,90 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3519</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Madiun</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>16.22174338827856</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3519</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Madiun</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3519</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Madiun</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1943971043358663</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3107,7 +5239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3167,6 +5299,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3524</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamongan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3181,7 +5341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3241,6 +5401,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3525</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Gresik</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3525</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Gresik</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1788899632423023</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3255,7 +5471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3315,6 +5531,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3527</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sampang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3329,7 +5573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3389,6 +5633,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3528</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pamekasan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.956440473627376</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3528</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pamekasan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3403,7 +5703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3701,20 +6001,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-2073185.822107816</v>
+        <v>2.4527928302494</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3729,20 +6029,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2127304.761456458</v>
+        <v>0.1160881198375328</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3757,18 +6057,186 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>38.29279213746975</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3506</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kediri</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3506</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kediri</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9.28453853138887</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3506</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kediri</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.249797778535008</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3506</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kediri</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-2073185.822107816</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3506</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kediri</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2127304.761456458</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3506</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Kediri</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>-545631.1011699911</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3785,7 +6253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3845,6 +6313,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3571</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Kediri</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3859,7 +6355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3919,6 +6415,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3573</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-8.883857009610647</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3573</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3933,7 +6485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3993,6 +6545,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3574</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.492312873946316</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3574</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>19.84180383452142</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3574</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.950263233823962</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4007,7 +6671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4067,6 +6731,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3575</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4081,7 +6773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4141,6 +6833,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3579</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-7.250437889051799</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3579</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3579</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.630629564108555</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3579</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.137276523740625</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4155,6 +6959,508 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.6090509000376688</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_ril vs y-on-y_pkp_q3-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.1166737060715463</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_ril vs c-to-c_pkp_q3-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.02153046759025114</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pkp_q3-25_ril vs sog_y-on-y_pkp_q3-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.042290573199311</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.07974623543335582</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3502</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Ponorogo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.110379904295347</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3502</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ponorogo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.024718332229971</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3502</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ponorogo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>61.81852521906599</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3502</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ponorogo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3502</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ponorogo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.414247773152667</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3523</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tuban</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-8.722685251696392</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3523</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tuban</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -4192,85 +7498,159 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Surabaya</t>
+          <t>Kota Mojokerto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.6090509000376688</v>
+        <v>0.1668454030803447</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q3-25_ril vs y-on-y_pkp_q3-25_rev</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nilai revisi dan nilai rilis beda arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Surabaya</t>
+          <t>Kota Mojokerto</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.1166737060715463</v>
+        <v>5.573235256248597</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q3-25_ril vs c-to-c_pkp_q3-25_rev</t>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nilai revisi dan nilai rilis beda arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Surabaya</t>
+          <t>Kota Mojokerto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02153046759025114</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q3-25_ril vs sog_y-on-y_pkp_q3-25_rev</t>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nilai revisi dan nilai rilis beda arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3522</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bojonegoro</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4285,7 +7665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4457,6 +7837,146 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3572</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Blitar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-8.08242015598702</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3572</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Blitar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.917643589896337</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3572</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Blitar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3572</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Blitar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.778825474220275</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3572</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Blitar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.9230247367322482</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4471,7 +7991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4909,18 +8429,158 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>5.57077596449919</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3513</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Probolinggo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>32.33442732359476</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3513</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Probolinggo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3513</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Probolinggo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>17.09218483544132</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3513</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Probolinggo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-10.19847717500174</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3513</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Probolinggo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>2.295640696917536</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4937,7 +8597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5025,6 +8685,118 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3526</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangkalan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-8.556416667972879</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3526</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangkalan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3526</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangkalan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.90394372983019</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3526</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangkalan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.685437095548366</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5039,7 +8811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5127,6 +8899,62 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3529</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumenep</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.904166988224769</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3529</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumenep</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5141,7 +8969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5383,18 +9211,102 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>3.30261564432487</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3508</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Lumajang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>30.39271320702301</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3508</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Lumajang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3508</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Lumajang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>-2.596199506501739</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -5411,7 +9323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5614,6 +9526,118 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3520</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Magetan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3520</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Magetan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9685553853582264</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3520</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Magetan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2169320821594614</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3520</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Magetan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.679748681299054</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
